--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54903BA2-E70A-40A0-871F-361CA13E277A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0B5165-7752-46FF-A50B-7F1D05571112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="182">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -599,6 +599,24 @@
   </si>
   <si>
     <t>Artificiais</t>
+  </si>
+  <si>
+    <t>usado.para</t>
+  </si>
+  <si>
+    <t>"Verificar requisitos"</t>
+  </si>
+  <si>
+    <t>"Distribuir luminárias"</t>
+  </si>
+  <si>
+    <t>"Verificar áreas"</t>
+  </si>
+  <si>
+    <t>"Colocar mobiliário"</t>
+  </si>
+  <si>
+    <t>"-"</t>
   </si>
 </sst>
 </file>
@@ -1112,14 +1130,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -1192,6 +1202,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1839,7 +1857,7 @@
       </c>
       <c r="B18" s="21">
         <f ca="1">NOW()</f>
-        <v>46195.427012499997</v>
+        <v>46195.433839120371</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>93</v>
@@ -2796,19 +2814,19 @@
     <cfRule type="duplicateValues" dxfId="10" priority="48"/>
     <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9 AA1:AA7 L8:O9 AA8:XFD9 B8:B9 A2:A9">
-    <cfRule type="cellIs" dxfId="0" priority="65" operator="equal">
+  <conditionalFormatting sqref="F7:F9 AA1:AA7 A2:A9 B8:B9 L8:O9 AA8:XFD9">
+    <cfRule type="cellIs" dxfId="8" priority="65" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="8" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="652"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="653"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="656"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="662"/>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3111,7 +3129,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3122,12 +3140,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="47" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" style="49" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="47" customWidth="1"/>
     <col min="4" max="4" width="6.42578125" style="47" customWidth="1"/>
     <col min="5" max="5" width="5.28515625" style="47" customWidth="1"/>
     <col min="6" max="6" width="3.28515625" style="47" customWidth="1"/>
@@ -3136,14 +3154,14 @@
     <col min="9" max="9" width="14.42578125" style="47" customWidth="1"/>
     <col min="10" max="10" width="4.140625" style="47" customWidth="1"/>
     <col min="11" max="11" width="8.28515625" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="47" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.28515625" style="47" customWidth="1"/>
-    <col min="15" max="15" width="14" style="47" customWidth="1"/>
-    <col min="16" max="16" width="5" style="47" customWidth="1"/>
-    <col min="17" max="17" width="59.7109375" style="47" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="47" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.5703125" style="47" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="47" customWidth="1"/>
+    <col min="16" max="16" width="3.28515625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="14" style="47" customWidth="1"/>
+    <col min="18" max="18" width="5" style="47" customWidth="1"/>
+    <col min="19" max="19" width="61.5703125" style="47" customWidth="1"/>
     <col min="20" max="20" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
@@ -3156,10 +3174,12 @@
     <col min="29" max="29" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.28515625" style="47"/>
+    <col min="32" max="32" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.28515625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="55" t="s">
         <v>11</v>
       </c>
@@ -3253,8 +3273,14 @@
       <c r="AE1" s="23" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF1" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG1" s="23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56">
         <v>1</v>
       </c>
@@ -3295,23 +3321,23 @@
         <v>10</v>
       </c>
       <c r="N2" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="Q2" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="P2" s="32" t="s">
+      <c r="R2" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="S2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="R2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T2" s="32" t="s">
         <v>10</v>
       </c>
@@ -3348,8 +3374,14 @@
       <c r="AE2" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF2" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG2" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>2</v>
       </c>
@@ -3390,23 +3422,23 @@
         <v>164</v>
       </c>
       <c r="N3" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="P3" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="25" t="s">
+      <c r="Q3" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="R3" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="25" t="s">
+      <c r="S3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T3" s="32" t="s">
         <v>10</v>
       </c>
@@ -3443,10 +3475,16 @@
       <c r="AE3" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF3" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="48" t="s">
         <v>117</v>
@@ -3485,23 +3523,23 @@
         <v>165</v>
       </c>
       <c r="N4" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="P4" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O4" s="25" t="s">
+      <c r="Q4" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="R4" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="25" t="s">
+      <c r="S4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T4" s="32" t="s">
         <v>10</v>
       </c>
@@ -3538,10 +3576,16 @@
       <c r="AE4" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF4" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="56">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="48" t="s">
         <v>117</v>
@@ -3580,23 +3624,23 @@
         <v>163</v>
       </c>
       <c r="N5" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="P5" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O5" s="25" t="s">
+      <c r="Q5" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="P5" s="32" t="s">
+      <c r="R5" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="S5" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="R5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T5" s="32" t="s">
         <v>10</v>
       </c>
@@ -3633,10 +3677,16 @@
       <c r="AE5" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF5" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG5" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="48" t="s">
         <v>118</v>
@@ -3675,23 +3725,23 @@
         <v>170</v>
       </c>
       <c r="N6" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="P6" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O6" s="25" t="s">
+      <c r="Q6" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="P6" s="32" t="s">
+      <c r="R6" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="S6" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="R6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S6" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T6" s="32" t="s">
         <v>10</v>
       </c>
@@ -3728,10 +3778,16 @@
       <c r="AE6" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF6" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG6" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="48" t="s">
         <v>119</v>
@@ -3770,23 +3826,23 @@
         <v>169</v>
       </c>
       <c r="N7" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="P7" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="Q7" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="P7" s="32" t="s">
+      <c r="R7" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="S7" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="R7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T7" s="32" t="s">
         <v>10</v>
       </c>
@@ -3823,10 +3879,16 @@
       <c r="AE7" s="25" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF7" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG7" s="25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="48" t="s">
         <v>156</v>
@@ -3865,23 +3927,23 @@
         <v>10</v>
       </c>
       <c r="N8" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="P8" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="O8" s="25" t="s">
+      <c r="Q8" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="P8" s="32" t="s">
+      <c r="R8" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="S8" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="R8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>10</v>
-      </c>
       <c r="T8" s="32" t="s">
         <v>10</v>
       </c>
@@ -3916,6 +3978,12 @@
         <v>10</v>
       </c>
       <c r="AE8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF8" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG8" s="25" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0B5165-7752-46FF-A50B-7F1D05571112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8947D22A-D8CA-4F09-BB30-03786B2C462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="184">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -337,9 +337,6 @@
     <t>ABNT</t>
   </si>
   <si>
-    <t>Arquitetura</t>
-  </si>
-  <si>
     <t>000 Translate Classe 5</t>
   </si>
   <si>
@@ -445,18 +442,12 @@
     <t>Declara a um Agente Artificial</t>
   </si>
   <si>
-    <t>Declara a um Agente Artificial Gherkin</t>
-  </si>
-  <si>
     <t>Declares to a Human Agent</t>
   </si>
   <si>
     <t>Declares to an Artificial Agent</t>
   </si>
   <si>
-    <t>Declares to an Artificial Agent Gherkin</t>
-  </si>
-  <si>
     <t>Declares an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
   </si>
   <si>
@@ -478,9 +469,6 @@
     <t>Declara a un agente artificial</t>
   </si>
   <si>
-    <t>Declara a un agente artificial Gherkin</t>
-  </si>
-  <si>
     <t>Declara un contenedor de información de acuerdo con la norma NBR 19650-1. Definición del proyecto.</t>
   </si>
   <si>
@@ -553,9 +541,6 @@
     <t>"Aslak Hellesøy"</t>
   </si>
   <si>
-    <t>"Linguagem de BDD (Behaviour-Driven Development) ou Desenvolvimento Dirigido por Comportamento. Auxilia equipes a identificar erros de requisitos."</t>
-  </si>
-  <si>
     <t>"Multimodal nativo"</t>
   </si>
   <si>
@@ -617,6 +602,27 @@
   </si>
   <si>
     <t>"-"</t>
+  </si>
+  <si>
+    <t>Declara a linguagem Gherkin, para processos BDD (Behaviour-Driven Development).</t>
+  </si>
+  <si>
+    <t>Declares the Gherkin language, for BDD (Behaviour-Driven Development) processes.</t>
+  </si>
+  <si>
+    <t>Multidisciplinar</t>
+  </si>
+  <si>
+    <t>Linguagens</t>
+  </si>
+  <si>
+    <t>"Linguagem de BDD Desenvolvimento Dirigido por Comportamento. Auxilia equipes a identificar erros de requisitos."</t>
+  </si>
+  <si>
+    <t>AG-05</t>
+  </si>
+  <si>
+    <t>AG-06</t>
   </si>
 </sst>
 </file>
@@ -1670,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1681,7 +1687,7 @@
         <v>49</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1689,10 +1695,10 @@
         <v>50</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1703,7 +1709,7 @@
         <v>33</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1715,7 +1721,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1727,7 +1733,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1738,7 +1744,7 @@
         <v>55</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1746,10 +1752,10 @@
         <v>56</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,7 +1766,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1771,7 +1777,7 @@
         <v>60</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1782,7 +1788,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1793,7 +1799,7 @@
         <v>60</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1804,7 +1810,7 @@
         <v>60</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1815,7 +1821,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1826,7 +1832,7 @@
         <v>60</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1837,7 +1843,7 @@
         <v>60</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1845,10 +1851,10 @@
         <v>67</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1857,45 +1863,45 @@
       </c>
       <c r="B18" s="21">
         <f ca="1">NOW()</f>
-        <v>46195.433839120371</v>
+        <v>46195.450380787035</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B20" s="21" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B21" s="21" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1906,7 +1912,7 @@
         <v>60</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1917,7 +1923,7 @@
         <v>60</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1925,10 +1931,10 @@
         <v>71</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -1940,19 +1946,19 @@
         <v>Formaliza las clases para agentes.</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="22" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize agent classes.</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1967,28 +1973,26 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="6.28515625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="5" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="7.42578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="14" customWidth="1"/>
+    <col min="13" max="13" width="5.5703125" style="13" customWidth="1"/>
+    <col min="14" max="14" width="5.85546875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11" style="2" customWidth="1"/>
     <col min="16" max="16" width="47.85546875" style="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="54.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" style="2" customWidth="1"/>
     <col min="19" max="19" width="6.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" style="14" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" style="14" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.28515625" style="60" customWidth="1"/>
-    <col min="24" max="24" width="6.140625" style="35" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3" style="34" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="6.42578125" style="35" customWidth="1"/>
+    <col min="26" max="26" width="4.140625" style="34" customWidth="1"/>
     <col min="27" max="27" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -2073,7 +2077,7 @@
         <v>87</v>
       </c>
       <c r="AA1" s="50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2081,19 +2085,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C2" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G2" s="39" t="s">
         <v>10</v>
@@ -2127,10 +2131,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="41" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q2" s="41" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="R2" s="42" t="s">
         <v>10</v>
@@ -2148,7 +2152,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W2" s="59" t="str">
         <f>CONCATENATE("Key-AGE-",A2)</f>
@@ -2164,7 +2168,7 @@
         <v>10</v>
       </c>
       <c r="AA2" s="41" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2172,19 +2176,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>10</v>
@@ -2218,10 +2222,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="41" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Q3" s="41" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="R3" s="42" t="s">
         <v>10</v>
@@ -2239,7 +2243,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" ref="W3:W9" si="6">CONCATENATE("Key-AGE-",A3)</f>
@@ -2255,7 +2259,7 @@
         <v>10</v>
       </c>
       <c r="AA3" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2263,19 +2267,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>10</v>
@@ -2309,10 +2313,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Q4" s="41" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="R4" s="42" t="s">
         <v>10</v>
@@ -2330,7 +2334,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2346,7 +2350,7 @@
         <v>10</v>
       </c>
       <c r="AA4" s="41" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2354,19 +2358,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>10</v>
@@ -2400,10 +2404,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="41" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="Q5" s="41" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="R5" s="42" t="s">
         <v>10</v>
@@ -2421,7 +2425,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2437,7 +2441,7 @@
         <v>10</v>
       </c>
       <c r="AA5" s="41" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2445,19 +2449,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>10</v>
@@ -2491,10 +2495,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="41" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="Q6" s="41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="R6" s="42" t="s">
         <v>10</v>
@@ -2512,7 +2516,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2528,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2539,16 +2543,16 @@
         <v>80</v>
       </c>
       <c r="C7" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>115</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>116</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>10</v>
@@ -2582,10 +2586,10 @@
         <v>Agente Humano</v>
       </c>
       <c r="P7" s="41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q7" s="41" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="R7" s="42" t="s">
         <v>10</v>
@@ -2603,7 +2607,7 @@
         <v>Humanos</v>
       </c>
       <c r="V7" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2619,7 +2623,7 @@
         <v>10</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2630,16 +2634,16 @@
         <v>80</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G8" s="39" t="s">
         <v>10</v>
@@ -2673,10 +2677,10 @@
         <v>Agente Artificial</v>
       </c>
       <c r="P8" s="41" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q8" s="41" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R8" s="42" t="s">
         <v>10</v>
@@ -2694,7 +2698,7 @@
         <v>Artificiais</v>
       </c>
       <c r="V8" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2710,7 +2714,7 @@
         <v>10</v>
       </c>
       <c r="AA8" s="41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2721,16 +2725,16 @@
         <v>80</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G9" s="39" t="s">
         <v>10</v>
@@ -2757,17 +2761,18 @@
       </c>
       <c r="N9" s="40" t="str">
         <f t="shared" ref="N9" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
-        <v>Artificiais</v>
+        <v>Linguagens</v>
       </c>
       <c r="O9" s="40" t="str">
         <f t="shared" ref="O9" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F9),"."," ")," De "," de "))</f>
         <v>Gherkin</v>
       </c>
       <c r="P9" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q9" s="41" t="s">
-        <v>135</v>
+        <v>177</v>
+      </c>
+      <c r="Q9" s="41" t="str">
+        <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
+        <v>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</v>
       </c>
       <c r="R9" s="42" t="s">
         <v>10</v>
@@ -2782,10 +2787,10 @@
       </c>
       <c r="U9" s="43" t="str">
         <f t="shared" ref="U9" si="22">SUBSTITUTE(E9, ".", " ")</f>
-        <v>Artificiais</v>
+        <v>Linguagens</v>
       </c>
       <c r="V9" s="41" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2801,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="AA9" s="41" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2814,7 +2819,7 @@
     <cfRule type="duplicateValues" dxfId="10" priority="48"/>
     <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9 AA1:AA7 A2:A9 B8:B9 L8:O9 AA8:XFD9">
+  <conditionalFormatting sqref="F7:F9 AA1:AA7 A2:A9 B8:B9 L8:O9 AA8:XFD8 AB9:XFD9">
     <cfRule type="cellIs" dxfId="8" priority="65" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -3161,7 +3166,7 @@
     <col min="16" max="16" width="3.28515625" style="47" customWidth="1"/>
     <col min="17" max="17" width="14" style="47" customWidth="1"/>
     <col min="18" max="18" width="5" style="47" customWidth="1"/>
-    <col min="19" max="19" width="61.5703125" style="47" customWidth="1"/>
+    <col min="19" max="19" width="48.140625" style="47" customWidth="1"/>
     <col min="20" max="20" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
@@ -3288,7 +3293,7 @@
         <v>83</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>10</v>
@@ -3327,16 +3332,16 @@
         <v>10</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="Q2" s="25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R2" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S2" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T2" s="32" t="s">
         <v>10</v>
@@ -3386,13 +3391,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E3" s="46" t="s">
         <v>83</v>
@@ -3407,37 +3412,37 @@
         <v>77</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J3" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="P3" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="K3" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="P3" s="32" t="s">
-        <v>154</v>
-      </c>
       <c r="Q3" s="25" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="R3" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="T3" s="32" t="s">
         <v>10</v>
@@ -3490,10 +3495,10 @@
         <v>117</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>83</v>
@@ -3508,37 +3513,37 @@
         <v>77</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J4" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="P4" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="K4" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="P4" s="32" t="s">
-        <v>154</v>
-      </c>
       <c r="Q4" s="25" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="T4" s="32" t="s">
         <v>10</v>
@@ -3588,13 +3593,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>83</v>
@@ -3609,37 +3614,37 @@
         <v>77</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J5" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="P5" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="K5" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>154</v>
-      </c>
       <c r="Q5" s="25" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="R5" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="T5" s="32" t="s">
         <v>10</v>
@@ -3689,13 +3694,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>83</v>
@@ -3710,37 +3715,37 @@
         <v>77</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J6" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="P6" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="P6" s="32" t="s">
-        <v>154</v>
-      </c>
       <c r="Q6" s="25" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="R6" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="T6" s="32" t="s">
         <v>10</v>
@@ -3790,13 +3795,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>120</v>
-      </c>
       <c r="D7" s="45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>83</v>
@@ -3811,37 +3816,37 @@
         <v>77</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J7" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="P7" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="P7" s="32" t="s">
-        <v>154</v>
-      </c>
       <c r="Q7" s="25" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="R7" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="T7" s="32" t="s">
         <v>10</v>
@@ -3891,13 +3896,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E8" s="46" t="s">
         <v>83</v>
@@ -3912,37 +3917,37 @@
         <v>77</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J8" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="P8" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="P8" s="32" t="s">
+      <c r="Q8" s="25" t="s">
         <v>154</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>158</v>
       </c>
       <c r="R8" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="T8" s="32" t="s">
         <v>10</v>

--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8947D22A-D8CA-4F09-BB30-03786B2C462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FAB593-0E79-4130-9230-D4F219558CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -511,9 +511,6 @@
     <t>"ChatGPT"</t>
   </si>
   <si>
-    <t>criador</t>
-  </si>
-  <si>
     <t>"Google DeepMind"</t>
   </si>
   <si>
@@ -577,18 +574,12 @@
     <t>"Agente de IA da Open"</t>
   </si>
   <si>
-    <t>modelo.usado</t>
-  </si>
-  <si>
     <t>Humanos</t>
   </si>
   <si>
     <t>Artificiais</t>
   </si>
   <si>
-    <t>usado.para</t>
-  </si>
-  <si>
     <t>"Verificar requisitos"</t>
   </si>
   <si>
@@ -623,6 +614,15 @@
   </si>
   <si>
     <t>AG-06</t>
+  </si>
+  <si>
+    <t>agente.modelo.usado</t>
+  </si>
+  <si>
+    <t>agente.finalidade</t>
+  </si>
+  <si>
+    <t>quem.criou</t>
   </si>
 </sst>
 </file>
@@ -1660,15 +1660,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="61" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.28515625" style="61"/>
+    <col min="1" max="1" width="9.3046875" style="61" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.3046875" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>46</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>48</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
         <v>50</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20" t="s">
         <v>51</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20" t="s">
         <v>52</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20" t="s">
         <v>53</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20" t="s">
         <v>54</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
         <v>56</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20" t="s">
         <v>57</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20" t="s">
         <v>59</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20" t="s">
         <v>61</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20" t="s">
         <v>62</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20" t="s">
         <v>63</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20" t="s">
         <v>64</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20" t="s">
         <v>65</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20" t="s">
         <v>66</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20" t="s">
         <v>67</v>
       </c>
@@ -1857,19 +1857,19 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="21">
         <f ca="1">NOW()</f>
-        <v>46195.450380787035</v>
+        <v>46213.74120300926</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20" t="s">
         <v>95</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20" t="s">
         <v>96</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20" t="s">
         <v>97</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20" t="s">
         <v>69</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20" t="s">
         <v>70</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="20" t="s">
         <v>71</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
         <v>72</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>90</v>
       </c>
@@ -1970,34 +1970,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" style="14" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="7.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" style="14" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" style="13" customWidth="1"/>
-    <col min="14" max="14" width="5.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.53515625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="5.3046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.3046875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="5.69140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="7.3828125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="5.53515625" style="14" customWidth="1"/>
+    <col min="13" max="13" width="5.53515625" style="13" customWidth="1"/>
+    <col min="14" max="14" width="5.84375" style="2" customWidth="1"/>
     <col min="15" max="15" width="11" style="2" customWidth="1"/>
-    <col min="16" max="16" width="47.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="54.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.28515625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.84375" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="54.3828125" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.3046875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="6.84375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="6.69140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.3046875" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="60" customWidth="1"/>
-    <col min="24" max="25" width="6.42578125" style="35" customWidth="1"/>
-    <col min="26" max="26" width="4.140625" style="34" customWidth="1"/>
-    <col min="27" max="27" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="2"/>
+    <col min="23" max="23" width="7.3046875" style="60" customWidth="1"/>
+    <col min="24" max="25" width="6.3828125" style="35" customWidth="1"/>
+    <col min="26" max="26" width="4.15234375" style="34" customWidth="1"/>
+    <col min="27" max="27" width="70.84375" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28">
         <v>0</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="36">
         <v>2</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W2" s="59" t="str">
         <f>CONCATENATE("Key-AGE-",A2)</f>
@@ -2171,7 +2171,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="36">
         <v>3</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" ref="W3:W9" si="6">CONCATENATE("Key-AGE-",A3)</f>
@@ -2262,7 +2262,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="36">
         <v>4</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2353,7 +2353,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="36">
         <v>5</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2444,7 +2444,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="36">
         <v>6</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2535,7 +2535,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="36">
         <v>7</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>111</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>115</v>
@@ -2607,7 +2607,7 @@
         <v>Humanos</v>
       </c>
       <c r="V7" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2626,7 +2626,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36">
         <v>8</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>111</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>119</v>
@@ -2698,7 +2698,7 @@
         <v>Artificiais</v>
       </c>
       <c r="V8" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2717,7 +2717,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="36">
         <v>9</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>111</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>120</v>
@@ -2768,7 +2768,7 @@
         <v>Gherkin</v>
       </c>
       <c r="P9" s="41" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Q9" s="41" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
@@ -2790,7 +2790,7 @@
         <v>Linguagens</v>
       </c>
       <c r="V9" s="41" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="6"/>
@@ -2806,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="AA9" s="41" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +2819,7 @@
     <cfRule type="duplicateValues" dxfId="10" priority="48"/>
     <cfRule type="duplicateValues" dxfId="9" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9 AA1:AA7 A2:A9 B8:B9 L8:O9 AA8:XFD8 AB9:XFD9">
+  <conditionalFormatting sqref="F7:F9 AA1:AA7 A2:A9 AA8:XFD8 B8:B9 L8:O9 AB9:XFD9">
     <cfRule type="cellIs" dxfId="8" priority="65" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -2842,15 +2842,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="10"/>
+    <col min="22" max="16384" width="11.15234375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -3055,16 +3055,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" customWidth="1"/>
+    <col min="3" max="3" width="10.69140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3046875" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15">
         <v>1</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="27">
         <v>3</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="27">
         <v>4</v>
       </c>
@@ -3146,45 +3146,45 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG8"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.28515625" style="49" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" style="47" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" style="47" customWidth="1"/>
-    <col min="6" max="6" width="3.28515625" style="47" customWidth="1"/>
-    <col min="7" max="7" width="2.5703125" style="47" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="47" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="47" customWidth="1"/>
-    <col min="10" max="10" width="4.140625" style="47" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="47" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.5703125" style="47" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" style="47" customWidth="1"/>
-    <col min="16" max="16" width="3.28515625" style="47" customWidth="1"/>
+    <col min="1" max="1" width="1.69140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.3046875" style="49" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" style="47" customWidth="1"/>
+    <col min="4" max="4" width="7.3046875" style="47" customWidth="1"/>
+    <col min="5" max="5" width="5.3046875" style="47" customWidth="1"/>
+    <col min="6" max="6" width="3.3046875" style="47" customWidth="1"/>
+    <col min="7" max="7" width="2.53515625" style="47" customWidth="1"/>
+    <col min="8" max="8" width="3.69140625" style="47" customWidth="1"/>
+    <col min="9" max="9" width="14.3828125" style="47" customWidth="1"/>
+    <col min="10" max="10" width="6.07421875" style="47" customWidth="1"/>
+    <col min="11" max="11" width="8.3046875" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.3828125" style="47" customWidth="1"/>
+    <col min="15" max="15" width="10.69140625" style="47" customWidth="1"/>
+    <col min="16" max="16" width="3.3046875" style="47" customWidth="1"/>
     <col min="17" max="17" width="14" style="47" customWidth="1"/>
     <col min="18" max="18" width="5" style="47" customWidth="1"/>
-    <col min="19" max="19" width="48.140625" style="47" customWidth="1"/>
-    <col min="20" max="20" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="2.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="1.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.28515625" style="47"/>
+    <col min="19" max="19" width="48.15234375" style="47" customWidth="1"/>
+    <col min="20" max="20" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="1.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.3046875" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="55" t="s">
         <v>11</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>1</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>10</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q2" s="25" t="s">
         <v>110</v>
@@ -3386,7 +3386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>2</v>
       </c>
@@ -3415,34 +3415,34 @@
         <v>143</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="K3" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="P3" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="L3" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="O3" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="P3" s="32" t="s">
-        <v>150</v>
-      </c>
       <c r="Q3" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R3" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="T3" s="32" t="s">
         <v>10</v>
@@ -3487,7 +3487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>3</v>
       </c>
@@ -3516,34 +3516,34 @@
         <v>143</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="K4" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="P4" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="L4" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="P4" s="32" t="s">
-        <v>150</v>
-      </c>
       <c r="Q4" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="T4" s="32" t="s">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>4</v>
       </c>
@@ -3617,34 +3617,34 @@
         <v>143</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="K5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="P5" s="32" t="s">
         <v>149</v>
       </c>
-      <c r="L5" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>150</v>
-      </c>
       <c r="Q5" s="25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R5" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="T5" s="32" t="s">
         <v>10</v>
@@ -3689,12 +3689,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>5</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>119</v>
@@ -3718,34 +3718,34 @@
         <v>144</v>
       </c>
       <c r="J6" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K6" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>147</v>
-      </c>
       <c r="L6" s="32" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P6" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R6" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T6" s="32" t="s">
         <v>10</v>
@@ -3790,12 +3790,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>6</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>119</v>
@@ -3819,34 +3819,34 @@
         <v>145</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L7" s="32" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N7" s="32" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="P7" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q7" s="25" t="s">
         <v>150</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>151</v>
       </c>
       <c r="R7" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T7" s="32" t="s">
         <v>10</v>
@@ -3891,12 +3891,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>7</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C8" s="38" t="s">
         <v>119</v>
@@ -3917,37 +3917,37 @@
         <v>77</v>
       </c>
       <c r="I8" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="O8" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="P8" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q8" s="25" t="s">
         <v>153</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="P8" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>154</v>
       </c>
       <c r="R8" s="32" t="s">
         <v>76</v>
       </c>
       <c r="S8" s="25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="T8" s="32" t="s">
         <v>10</v>

--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30FAB593-0E79-4130-9230-D4F219558CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C405EA5-E1F6-4D64-A219-EC4ADC0EC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B18" s="21">
         <f ca="1">NOW()</f>
-        <v>46213.74120300926</v>
+        <v>46214.408310416664</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>92</v>
@@ -3149,24 +3149,24 @@
   <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.69140625" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.3046875" style="49" customWidth="1"/>
-    <col min="3" max="3" width="7.3828125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="7.3046875" style="47" customWidth="1"/>
-    <col min="5" max="5" width="5.3046875" style="47" customWidth="1"/>
-    <col min="6" max="6" width="3.3046875" style="47" customWidth="1"/>
+    <col min="2" max="2" width="4.61328125" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="2.53515625" style="47" customWidth="1"/>
-    <col min="8" max="8" width="3.69140625" style="47" customWidth="1"/>
+    <col min="8" max="8" width="2.61328125" style="47" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.3828125" style="47" customWidth="1"/>
-    <col min="10" max="10" width="6.07421875" style="47" customWidth="1"/>
+    <col min="10" max="10" width="4.69140625" style="47" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.3046875" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.3828125" style="47" customWidth="1"/>
-    <col min="15" max="15" width="10.69140625" style="47" customWidth="1"/>
-    <col min="16" max="16" width="3.3046875" style="47" customWidth="1"/>
-    <col min="17" max="17" width="14" style="47" customWidth="1"/>
+    <col min="12" max="12" width="8.53515625" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.07421875" style="47" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.765625" style="47" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.61328125" style="47" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" style="47" customWidth="1"/>
-    <col min="19" max="19" width="48.15234375" style="47" customWidth="1"/>
+    <col min="19" max="19" width="45.69140625" style="47" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="1.84375" style="47" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="2.3828125" style="47" bestFit="1" customWidth="1"/>

--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C405EA5-E1F6-4D64-A219-EC4ADC0EC9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0AA766-3C6E-444B-8899-1D8B73D3D348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="174">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -313,9 +313,6 @@
     <t>Equivalente a</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>órgão</t>
   </si>
   <si>
@@ -379,12 +376,6 @@
     <t>"Contêiner do Inventário de todas as informações espaciais do Projeto"</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
@@ -397,9 +388,6 @@
     <t>Requisito.Sistemas</t>
   </si>
   <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Gestão</t>
   </si>
   <si>
@@ -448,57 +436,12 @@
     <t>Declares to an Artificial Agent</t>
   </si>
   <si>
-    <t>Declares an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
-  </si>
-  <si>
-    <t>Declares an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</t>
-  </si>
-  <si>
-    <t>Declares an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</t>
-  </si>
-  <si>
-    <t>Declares an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</t>
-  </si>
-  <si>
-    <t>Declares an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
-  </si>
-  <si>
     <t>Declara a un agente humano</t>
   </si>
   <si>
     <t>Declara a un agente artificial</t>
   </si>
   <si>
-    <t>Declara un contenedor de información de acuerdo con la norma NBR 19650-1. Definición del proyecto.</t>
-  </si>
-  <si>
-    <t>Declara un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos espaciales para el proyecto.</t>
-  </si>
-  <si>
-    <t>Declara un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de mobiliario para el proyecto.</t>
-  </si>
-  <si>
-    <t>Declara un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de equipamiento para el proyecto.</t>
-  </si>
-  <si>
-    <t>Declara un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</t>
-  </si>
-  <si>
-    <t>Declara um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Declara um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Declara um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Declara um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Declara um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>é.agente.de</t>
   </si>
   <si>
@@ -601,9 +544,6 @@
     <t>Declares the Gherkin language, for BDD (Behaviour-Driven Development) processes.</t>
   </si>
   <si>
-    <t>Multidisciplinar</t>
-  </si>
-  <si>
     <t>Linguagens</t>
   </si>
   <si>
@@ -623,6 +563,36 @@
   </si>
   <si>
     <t>quem.criou</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Interdisciplinar</t>
   </si>
 </sst>
 </file>
@@ -947,7 +917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1125,18 +1095,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="16">
     <dxf>
       <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1256,6 +1237,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1660,15 +1659,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="61" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.3046875" style="61"/>
+    <col min="1" max="1" width="9.28515625" style="61" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.28515625" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>46</v>
       </c>
@@ -1676,10 +1675,10 @@
         <v>47</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>48</v>
       </c>
@@ -1687,21 +1686,21 @@
         <v>49</v>
       </c>
       <c r="C2" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>51</v>
       </c>
@@ -1709,10 +1708,10 @@
         <v>33</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>52</v>
       </c>
@@ -1721,10 +1720,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>53</v>
       </c>
@@ -1733,10 +1732,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>54</v>
       </c>
@@ -1744,21 +1743,21 @@
         <v>55</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>57</v>
       </c>
@@ -1766,10 +1765,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>59</v>
       </c>
@@ -1777,10 +1776,10 @@
         <v>60</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>61</v>
       </c>
@@ -1788,10 +1787,10 @@
         <v>60</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>62</v>
       </c>
@@ -1799,10 +1798,10 @@
         <v>60</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>63</v>
       </c>
@@ -1810,10 +1809,10 @@
         <v>60</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>64</v>
       </c>
@@ -1821,10 +1820,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>65</v>
       </c>
@@ -1832,10 +1831,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>66</v>
       </c>
@@ -1843,68 +1842,68 @@
         <v>60</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="21">
         <f ca="1">NOW()</f>
-        <v>46214.408310416664</v>
+        <v>46216.366567824072</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
         <v>95</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="20" t="s">
-        <v>96</v>
       </c>
       <c r="B20" s="21" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" s="21" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>69</v>
       </c>
@@ -1912,10 +1911,10 @@
         <v>60</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>70</v>
       </c>
@@ -1923,21 +1922,21 @@
         <v>60</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>71</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>72</v>
       </c>
@@ -1946,19 +1945,19 @@
         <v>Formaliza las clases para agentes.</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B26" s="22" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize agent classes.</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1970,34 +1969,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.53515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="5.3046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.3046875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="5.69140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="7.3828125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.53515625" style="14" customWidth="1"/>
-    <col min="13" max="13" width="5.53515625" style="13" customWidth="1"/>
-    <col min="14" max="14" width="5.84375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11" style="2" customWidth="1"/>
-    <col min="16" max="16" width="47.84375" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="54.3828125" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.3046875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="6.84375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="6.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.28515625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.3046875" style="60" customWidth="1"/>
-    <col min="24" max="25" width="6.3828125" style="35" customWidth="1"/>
-    <col min="26" max="26" width="4.15234375" style="34" customWidth="1"/>
-    <col min="27" max="27" width="70.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="2"/>
+    <col min="23" max="23" width="7.7109375" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28">
         <v>0</v>
       </c>
@@ -2049,7 +2048,7 @@
       <c r="Q1" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="62" t="s">
         <v>40</v>
       </c>
       <c r="S1" s="17" t="s">
@@ -2068,36 +2067,36 @@
         <v>9</v>
       </c>
       <c r="X1" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y1" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="Y1" s="33" t="s">
+      <c r="Z1" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="Z1" s="54" t="s">
+      <c r="AA1" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="AA1" s="50" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36">
         <v>2</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>100</v>
+        <v>164</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>105</v>
       </c>
       <c r="D2" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" s="38" t="s">
         <v>99</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="38" t="s">
-        <v>108</v>
       </c>
       <c r="G2" s="39" t="s">
         <v>10</v>
@@ -2116,7 +2115,7 @@
       </c>
       <c r="L2" s="40" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M2" s="40" t="str">
         <f t="shared" si="0"/>
@@ -2124,24 +2123,24 @@
       </c>
       <c r="N2" s="40" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O2" s="40" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
+        <v>Contêiner</v>
       </c>
       <c r="P2" s="41" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="Q2" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="R2" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="R2" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S2" s="43" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T2" s="43" t="str">
         <f t="shared" si="2"/>
@@ -2149,14 +2148,14 @@
       </c>
       <c r="U2" s="43" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V2" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="W2" s="59" t="str">
-        <f>CONCATENATE("Key-AGE-",A2)</f>
-        <v>Key-AGE-2</v>
+        <f>CONCATENATE("Key-AGEN-",A2)</f>
+        <v>Key-AGEN-2</v>
       </c>
       <c r="X2" s="41" t="s">
         <v>10</v>
@@ -2165,30 +2164,31 @@
         <v>10</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA2" s="41" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>168</v>
+      </c>
+      <c r="AA2" s="41" t="str">
+        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <v>3</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>100</v>
+        <v>164</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>105</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>165</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="L3" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M3" s="40" t="str">
         <f t="shared" si="0"/>
@@ -2215,71 +2215,72 @@
       </c>
       <c r="N3" s="40" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O3" s="40" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="41" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="Q3" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="R3" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="R3" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S3" s="43" t="str">
-        <f t="shared" ref="S3:S5" si="3">SUBSTITUTE(C3, ".", " ")</f>
-        <v>Contêiner</v>
+        <f t="shared" si="2"/>
+        <v>Gestão</v>
       </c>
       <c r="T3" s="43" t="str">
-        <f t="shared" ref="T3:T5" si="4">SUBSTITUTE(D3, ".", " ")</f>
+        <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
       <c r="U3" s="43" t="str">
-        <f t="shared" ref="U3:U5" si="5">SUBSTITUTE(E3, ".", " ")</f>
-        <v>Requerida</v>
+        <f t="shared" si="2"/>
+        <v>Contêineres</v>
       </c>
       <c r="V3" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="W3" s="59" t="str">
-        <f t="shared" ref="W3:W9" si="6">CONCATENATE("Key-AGE-",A3)</f>
-        <v>Key-AGE-3</v>
+        <f t="shared" ref="W3:W9" si="4">CONCATENATE("Key-AGEN-",A3)</f>
+        <v>Key-AGEN-3</v>
       </c>
       <c r="X3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="Y3" s="41" t="s">
+      <c r="Y3" s="43" t="s">
         <v>10</v>
       </c>
       <c r="Z3" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="AA3" s="41" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AA3" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <v>4</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>100</v>
+        <v>164</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>105</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="38" t="s">
         <v>102</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>105</v>
       </c>
       <c r="G4" s="39" t="s">
         <v>10</v>
@@ -2298,7 +2299,7 @@
       </c>
       <c r="L4" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M4" s="40" t="str">
         <f t="shared" si="0"/>
@@ -2306,71 +2307,72 @@
       </c>
       <c r="N4" s="40" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O4" s="40" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="Q4" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="R4" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="R4" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S4" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U4" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="W4" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-4</v>
+      </c>
+      <c r="X4" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y4" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="43" t="str">
-        <f t="shared" si="4"/>
-        <v>Informação</v>
-      </c>
-      <c r="U4" s="43" t="str">
-        <f t="shared" si="5"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="W4" s="59" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-AGE-4</v>
-      </c>
-      <c r="X4" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y4" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z4" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="41" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <v>5</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>100</v>
+        <v>164</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>105</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>165</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G5" s="39" t="s">
         <v>10</v>
@@ -2389,7 +2391,7 @@
       </c>
       <c r="L5" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M5" s="40" t="str">
         <f t="shared" si="0"/>
@@ -2397,71 +2399,72 @@
       </c>
       <c r="N5" s="40" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O5" s="40" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="41" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="Q5" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="R5" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="R5" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S5" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U5" s="43" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="W5" s="59" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-5</v>
+      </c>
+      <c r="X5" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="41" t="str">
         <f t="shared" si="3"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="43" t="str">
-        <f t="shared" si="4"/>
-        <v>Informação</v>
-      </c>
-      <c r="U5" s="43" t="str">
-        <f t="shared" si="5"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="41" t="s">
-        <v>176</v>
-      </c>
-      <c r="W5" s="59" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-AGE-5</v>
-      </c>
-      <c r="X5" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="41" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>6</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>100</v>
+        <v>164</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>105</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>165</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G6" s="39" t="s">
         <v>10</v>
@@ -2480,7 +2483,7 @@
       </c>
       <c r="L6" s="40" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="M6" s="40" t="str">
         <f t="shared" si="0"/>
@@ -2488,24 +2491,24 @@
       </c>
       <c r="N6" s="40" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="O6" s="40" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="41" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="Q6" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="R6" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="R6" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S6" s="43" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
+        <v>Gestão</v>
       </c>
       <c r="T6" s="43" t="str">
         <f t="shared" si="2"/>
@@ -2513,47 +2516,48 @@
       </c>
       <c r="U6" s="43" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
+        <v>Contêineres</v>
       </c>
       <c r="V6" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="W6" s="59" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-AGE-6</v>
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-6</v>
       </c>
       <c r="X6" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="Y6" s="41" t="s">
+      <c r="Y6" s="43" t="s">
         <v>10</v>
       </c>
       <c r="Z6" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="AA6" s="41" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AA6" s="41" t="str">
+        <f t="shared" si="3"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
         <v>7</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D7" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>115</v>
-      </c>
       <c r="G7" s="39" t="s">
         <v>10</v>
       </c>
@@ -2570,48 +2574,48 @@
         <v>10</v>
       </c>
       <c r="L7" s="40" t="str">
-        <f t="shared" ref="L7" si="7">CONCATENATE("", C7)</f>
+        <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
         <v>Agência</v>
       </c>
       <c r="M7" s="40" t="str">
-        <f t="shared" ref="M7" si="8">CONCATENATE("", D7)</f>
+        <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
         <v>Agentes</v>
       </c>
       <c r="N7" s="40" t="str">
-        <f t="shared" ref="N7:O7" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N7:O7" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Humanos</v>
       </c>
       <c r="O7" s="40" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>Agente Humano</v>
       </c>
       <c r="P7" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q7" s="41" t="s">
         <v>121</v>
       </c>
-      <c r="Q7" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S7" s="43" t="str">
-        <f t="shared" ref="S7:U7" si="10">SUBSTITUTE(C7, ".", " ")</f>
+        <f t="shared" ref="S7:U7" si="8">SUBSTITUTE(C7, ".", " ")</f>
         <v>Agência</v>
       </c>
       <c r="T7" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>Agentes</v>
       </c>
       <c r="U7" s="43" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>Humanos</v>
       </c>
       <c r="V7" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="W7" s="59" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-AGE-7</v>
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-7</v>
       </c>
       <c r="X7" s="41" t="s">
         <v>10</v>
@@ -2623,27 +2627,27 @@
         <v>10</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>8</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G8" s="39" t="s">
         <v>10</v>
@@ -2661,48 +2665,48 @@
         <v>10</v>
       </c>
       <c r="L8" s="40" t="str">
-        <f t="shared" ref="L8:M8" si="11">CONCATENATE("", C8)</f>
+        <f t="shared" ref="L8:M8" si="9">CONCATENATE("", C8)</f>
         <v>Agência</v>
       </c>
       <c r="M8" s="40" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>Agentes</v>
       </c>
       <c r="N8" s="40" t="str">
-        <f t="shared" ref="N8:O8" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N8:O8" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
         <v>Artificiais</v>
       </c>
       <c r="O8" s="40" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>Agente Artificial</v>
       </c>
       <c r="P8" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q8" s="41" t="s">
         <v>122</v>
       </c>
-      <c r="Q8" s="41" t="s">
-        <v>131</v>
-      </c>
-      <c r="R8" s="42" t="s">
+      <c r="R8" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S8" s="43" t="str">
-        <f t="shared" ref="S8" si="13">SUBSTITUTE(C8, ".", " ")</f>
+        <f t="shared" ref="S8" si="11">SUBSTITUTE(C8, ".", " ")</f>
         <v>Agência</v>
       </c>
       <c r="T8" s="43" t="str">
-        <f t="shared" ref="T8" si="14">SUBSTITUTE(D8, ".", " ")</f>
+        <f t="shared" ref="T8" si="12">SUBSTITUTE(D8, ".", " ")</f>
         <v>Agentes</v>
       </c>
       <c r="U8" s="43" t="str">
-        <f t="shared" ref="U8" si="15">SUBSTITUTE(E8, ".", " ")</f>
+        <f t="shared" ref="U8" si="13">SUBSTITUTE(E8, ".", " ")</f>
         <v>Artificiais</v>
       </c>
       <c r="V8" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="W8" s="59" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-AGE-8</v>
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-8</v>
       </c>
       <c r="X8" s="41" t="s">
         <v>10</v>
@@ -2714,27 +2718,27 @@
         <v>10</v>
       </c>
       <c r="AA8" s="41" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
         <v>9</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G9" s="39" t="s">
         <v>10</v>
@@ -2752,49 +2756,49 @@
         <v>10</v>
       </c>
       <c r="L9" s="40" t="str">
-        <f t="shared" ref="L9" si="16">CONCATENATE("", C9)</f>
+        <f t="shared" ref="L9" si="14">CONCATENATE("", C9)</f>
         <v>Agência</v>
       </c>
       <c r="M9" s="40" t="str">
-        <f t="shared" ref="M9" si="17">CONCATENATE("", D9)</f>
+        <f t="shared" ref="M9" si="15">CONCATENATE("", D9)</f>
         <v>Agentes</v>
       </c>
       <c r="N9" s="40" t="str">
-        <f t="shared" ref="N9" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N9" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
         <v>Linguagens</v>
       </c>
       <c r="O9" s="40" t="str">
-        <f t="shared" ref="O9" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F9),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O9" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F9),"."," ")," De "," de "))</f>
         <v>Gherkin</v>
       </c>
       <c r="P9" s="41" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="Q9" s="41" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
         <v>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</v>
       </c>
-      <c r="R9" s="42" t="s">
+      <c r="R9" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S9" s="43" t="str">
-        <f t="shared" ref="S9" si="20">SUBSTITUTE(C9, ".", " ")</f>
+        <f t="shared" ref="S9" si="18">SUBSTITUTE(C9, ".", " ")</f>
         <v>Agência</v>
       </c>
       <c r="T9" s="43" t="str">
-        <f t="shared" ref="T9" si="21">SUBSTITUTE(D9, ".", " ")</f>
+        <f t="shared" ref="T9" si="19">SUBSTITUTE(D9, ".", " ")</f>
         <v>Agentes</v>
       </c>
       <c r="U9" s="43" t="str">
-        <f t="shared" ref="U9" si="22">SUBSTITUTE(E9, ".", " ")</f>
+        <f t="shared" ref="U9" si="20">SUBSTITUTE(E9, ".", " ")</f>
         <v>Linguagens</v>
       </c>
       <c r="V9" s="41" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="W9" s="59" t="str">
-        <f t="shared" si="6"/>
-        <v>Key-AGE-9</v>
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-9</v>
       </c>
       <c r="X9" s="41" t="s">
         <v>10</v>
@@ -2806,32 +2810,43 @@
         <v>10</v>
       </c>
       <c r="AA9" s="41" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+  <conditionalFormatting sqref="A2:B9">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="11" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="49"/>
+  <conditionalFormatting sqref="F1 F7:F1048576">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9 AA1:AA7 A2:A9 AA8:XFD8 B8:B9 L8:O9 AB9:XFD9">
-    <cfRule type="cellIs" dxfId="8" priority="65" operator="equal">
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F9 AA8:XFD8 L8:O9 AB9:XFD9">
+    <cfRule type="cellIs" dxfId="9" priority="71" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="7" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="652"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="653"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="626"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="668"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA7">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2842,15 +2857,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="10"/>
+    <col min="22" max="16384" width="11.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -2915,7 +2930,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -2980,7 +2995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -3055,16 +3070,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15">
         <v>1</v>
       </c>
@@ -3081,7 +3096,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -3098,7 +3113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>3</v>
       </c>
@@ -3115,7 +3130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="27">
         <v>4</v>
       </c>
@@ -3145,46 +3160,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:AG8"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q8"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.69140625" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.61328125" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.53515625" style="47" customWidth="1"/>
-    <col min="8" max="8" width="2.61328125" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.3828125" style="47" customWidth="1"/>
-    <col min="10" max="10" width="4.69140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.3046875" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.53515625" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.07421875" style="47" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.765625" style="47" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.61328125" style="47" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5" style="47" customWidth="1"/>
-    <col min="19" max="19" width="45.69140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="2.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="1.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.3046875" style="47"/>
+    <col min="1" max="1" width="2.5703125" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" style="49" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="47" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="47" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" style="47" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="47" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="47" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="47" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="47" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" style="47" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="47" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" style="47" customWidth="1"/>
+    <col min="17" max="17" width="49.5703125" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="9.28515625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="55" t="s">
         <v>11</v>
       </c>
@@ -3200,13 +3199,13 @@
       <c r="E1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="26" t="s">
         <v>75</v>
       </c>
       <c r="G1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="23" t="s">
         <v>75</v>
       </c>
       <c r="I1" s="23" t="s">
@@ -3236,88 +3235,40 @@
       <c r="Q1" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="R1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="S1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="T1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="U1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="V1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="W1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="X1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE1" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF1" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG1" s="23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56">
         <v>1</v>
       </c>
       <c r="B2" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="32" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>10</v>
@@ -3326,670 +3277,334 @@
         <v>10</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="P2" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q2" s="25" t="s">
-        <v>110</v>
-      </c>
-      <c r="R2" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="T2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG2" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Q2" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="46" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="L3" s="32" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="M3" s="25" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="N3" s="32" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="O3" s="25" t="s">
-        <v>170</v>
+        <v>137</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R3" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="S3" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="T3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF3" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG3" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>3</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D4" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="P4" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R4" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="T4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF4" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG4" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="56">
         <v>4</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D5" s="45" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="46" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="I5" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="O5" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="P5" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="J5" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="R5" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="T5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE5" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG5" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
         <v>5</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="F6" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="K6" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="P6" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q6" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="L6" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="P6" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="R6" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="S6" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="T6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE6" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF6" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG6" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>6</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="46" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>126</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="K7" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="L7" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="O7" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="P7" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="L7" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>173</v>
-      </c>
-      <c r="P7" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="R7" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="T7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE7" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF7" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG7" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>7</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>10</v>
+        <v>82</v>
+      </c>
+      <c r="F8" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>183</v>
+        <v>10</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>154</v>
+        <v>10</v>
       </c>
       <c r="L8" s="32" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="N8" s="32" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="O8" s="25" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="P8" s="32" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="R8" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="S8" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="T8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="U8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="V8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="W8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="X8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG8" s="25" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0AA766-3C6E-444B-8899-1D8B73D3D348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACBBA2B-D62A-4C0A-906F-20B015D07F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -403,9 +403,6 @@
     <t>Formalizar as classes de agentes.</t>
   </si>
   <si>
-    <t>Agência</t>
-  </si>
-  <si>
     <t>Agente.Humano</t>
   </si>
   <si>
@@ -565,9 +562,6 @@
     <t>quem.criou</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -593,6 +587,12 @@
   </si>
   <si>
     <t>Interdisciplinar</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Agênticos</t>
   </si>
 </sst>
 </file>
@@ -1659,15 +1659,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="61" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.28515625" style="61"/>
+    <col min="1" max="1" width="9.3046875" style="61" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.3046875" style="61"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>46</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>48</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
         <v>50</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20" t="s">
         <v>51</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20" t="s">
         <v>52</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20" t="s">
         <v>53</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20" t="s">
         <v>54</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
         <v>56</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20" t="s">
         <v>57</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20" t="s">
         <v>59</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20" t="s">
         <v>61</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20" t="s">
         <v>62</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20" t="s">
         <v>63</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20" t="s">
         <v>64</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20" t="s">
         <v>65</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20" t="s">
         <v>66</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20" t="s">
         <v>67</v>
       </c>
@@ -1856,19 +1856,19 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="21">
         <f ca="1">NOW()</f>
-        <v>46216.366567824072</v>
+        <v>46243.449320254629</v>
       </c>
       <c r="C18" s="52" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20" t="s">
         <v>94</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20" t="s">
         <v>95</v>
       </c>
@@ -1891,7 +1891,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20" t="s">
         <v>96</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20" t="s">
         <v>69</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20" t="s">
         <v>70</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="20" t="s">
         <v>71</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
         <v>72</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>89</v>
       </c>
@@ -1969,34 +1969,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="51.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.28515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.69140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.3046875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="8.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.53515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.53515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.53515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.61328125" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.7109375" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="6.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="2"/>
+    <col min="20" max="20" width="6.69140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.07421875" style="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.69140625" style="60" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28">
         <v>0</v>
       </c>
@@ -2079,12 +2079,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="36">
         <v>2</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C2" s="37" t="s">
         <v>105</v>
@@ -2093,7 +2093,7 @@
         <v>98</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>99</v>
@@ -2130,10 +2130,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q2" s="41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R2" s="43" t="s">
         <v>10</v>
@@ -2151,7 +2151,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W2" s="59" t="str">
         <f>CONCATENATE("Key-AGEN-",A2)</f>
@@ -2164,19 +2164,19 @@
         <v>10</v>
       </c>
       <c r="Z2" s="42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AA2" s="41" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="36">
         <v>3</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C3" s="37" t="s">
         <v>105</v>
@@ -2185,7 +2185,7 @@
         <v>98</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>101</v>
@@ -2222,10 +2222,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q3" s="41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R3" s="43" t="s">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W3" s="59" t="str">
         <f t="shared" ref="W3:W9" si="4">CONCATENATE("Key-AGEN-",A3)</f>
@@ -2263,12 +2263,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="36">
         <v>4</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C4" s="37" t="s">
         <v>105</v>
@@ -2277,7 +2277,7 @@
         <v>98</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>102</v>
@@ -2314,10 +2314,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="41" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="Q4" s="41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R4" s="43" t="s">
         <v>10</v>
@@ -2335,7 +2335,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W4" s="59" t="str">
         <f t="shared" si="4"/>
@@ -2355,12 +2355,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="36">
         <v>5</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C5" s="37" t="s">
         <v>105</v>
@@ -2369,7 +2369,7 @@
         <v>98</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>103</v>
@@ -2406,10 +2406,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="41" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="Q5" s="41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R5" s="43" t="s">
         <v>10</v>
@@ -2427,7 +2427,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W5" s="59" t="str">
         <f t="shared" si="4"/>
@@ -2447,12 +2447,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="36">
         <v>6</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C6" s="37" t="s">
         <v>105</v>
@@ -2461,7 +2461,7 @@
         <v>98</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>104</v>
@@ -2498,10 +2498,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="Q6" s="41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="R6" s="43" t="s">
         <v>10</v>
@@ -2519,7 +2519,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W6" s="59" t="str">
         <f t="shared" si="4"/>
@@ -2539,24 +2539,24 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="36">
         <v>7</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="D7" s="37" t="s">
         <v>107</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>10</v>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="L7" s="40" t="str">
         <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
-        <v>Agência</v>
+        <v>Agênticos</v>
       </c>
       <c r="M7" s="40" t="str">
         <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
@@ -2590,17 +2590,17 @@
         <v>Agente Humano</v>
       </c>
       <c r="P7" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q7" s="41" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R7" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S7" s="43" t="str">
         <f t="shared" ref="S7:U7" si="8">SUBSTITUTE(C7, ".", " ")</f>
-        <v>Agência</v>
+        <v>Agênticos</v>
       </c>
       <c r="T7" s="43" t="str">
         <f t="shared" si="8"/>
@@ -2611,7 +2611,7 @@
         <v>Humanos</v>
       </c>
       <c r="V7" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W7" s="59" t="str">
         <f t="shared" si="4"/>
@@ -2627,27 +2627,27 @@
         <v>10</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36">
         <v>8</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="D8" s="37" t="s">
         <v>107</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G8" s="39" t="s">
         <v>10</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="L8" s="40" t="str">
         <f t="shared" ref="L8:M8" si="9">CONCATENATE("", C8)</f>
-        <v>Agência</v>
+        <v>Agênticos</v>
       </c>
       <c r="M8" s="40" t="str">
         <f t="shared" si="9"/>
@@ -2681,17 +2681,17 @@
         <v>Agente Artificial</v>
       </c>
       <c r="P8" s="41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q8" s="41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="R8" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S8" s="43" t="str">
         <f t="shared" ref="S8" si="11">SUBSTITUTE(C8, ".", " ")</f>
-        <v>Agência</v>
+        <v>Agênticos</v>
       </c>
       <c r="T8" s="43" t="str">
         <f t="shared" ref="T8" si="12">SUBSTITUTE(D8, ".", " ")</f>
@@ -2702,7 +2702,7 @@
         <v>Artificiais</v>
       </c>
       <c r="V8" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W8" s="59" t="str">
         <f t="shared" si="4"/>
@@ -2718,27 +2718,27 @@
         <v>10</v>
       </c>
       <c r="AA8" s="41" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="36">
         <v>9</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="D9" s="37" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G9" s="39" t="s">
         <v>10</v>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="L9" s="40" t="str">
         <f t="shared" ref="L9" si="14">CONCATENATE("", C9)</f>
-        <v>Agência</v>
+        <v>Agênticos</v>
       </c>
       <c r="M9" s="40" t="str">
         <f t="shared" ref="M9" si="15">CONCATENATE("", D9)</f>
@@ -2772,7 +2772,7 @@
         <v>Gherkin</v>
       </c>
       <c r="P9" s="41" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q9" s="41" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="S9" s="43" t="str">
         <f t="shared" ref="S9" si="18">SUBSTITUTE(C9, ".", " ")</f>
-        <v>Agência</v>
+        <v>Agênticos</v>
       </c>
       <c r="T9" s="43" t="str">
         <f t="shared" ref="T9" si="19">SUBSTITUTE(D9, ".", " ")</f>
@@ -2794,7 +2794,7 @@
         <v>Linguagens</v>
       </c>
       <c r="V9" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="W9" s="59" t="str">
         <f t="shared" si="4"/>
@@ -2810,7 +2810,7 @@
         <v>10</v>
       </c>
       <c r="AA9" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2857,15 +2857,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="10"/>
+    <col min="22" max="16384" width="11.15234375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -3070,16 +3070,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" customWidth="1"/>
+    <col min="3" max="3" width="10.69140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3046875" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15">
         <v>1</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="27">
         <v>2</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="27">
         <v>3</v>
       </c>
@@ -3130,7 +3130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="27">
         <v>4</v>
       </c>
@@ -3161,29 +3161,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.140625" style="49" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="47" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" style="47" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" style="47" customWidth="1"/>
-    <col min="6" max="6" width="3.7109375" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="47" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="47" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="47" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="47" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" style="47" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="47" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" style="47" customWidth="1"/>
-    <col min="17" max="17" width="49.5703125" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="9.28515625" style="47"/>
+    <col min="1" max="1" width="2.53515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.15234375" style="49" customWidth="1"/>
+    <col min="3" max="3" width="7.69140625" style="47" customWidth="1"/>
+    <col min="4" max="4" width="5.84375" style="47" customWidth="1"/>
+    <col min="5" max="5" width="5.3046875" style="47" customWidth="1"/>
+    <col min="6" max="6" width="3.69140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.15234375" style="47" customWidth="1"/>
+    <col min="8" max="8" width="6.53515625" style="47" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.69140625" style="47" customWidth="1"/>
+    <col min="10" max="10" width="10.15234375" style="47" customWidth="1"/>
+    <col min="11" max="11" width="9.84375" style="47" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.69140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.3046875" style="47" customWidth="1"/>
+    <col min="14" max="14" width="3.15234375" style="47" customWidth="1"/>
+    <col min="15" max="15" width="14.15234375" style="47" customWidth="1"/>
+    <col min="16" max="16" width="5.15234375" style="47" customWidth="1"/>
+    <col min="17" max="17" width="49.53515625" style="47" customWidth="1"/>
+    <col min="18" max="16384" width="9.3046875" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="55" t="s">
         <v>11</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>1</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>10</v>
       </c>
       <c r="N2" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O2" s="25" t="s">
         <v>106</v>
@@ -3289,18 +3289,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E3" s="46" t="s">
         <v>82</v>
@@ -3309,51 +3309,51 @@
         <v>77</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I3" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="J3" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="K3" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="M3" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="N3" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>130</v>
-      </c>
       <c r="O3" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>76</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>3</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>82</v>
@@ -3362,51 +3362,51 @@
         <v>77</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I4" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="J4" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="L4" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="N4" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="J4" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>130</v>
-      </c>
       <c r="O4" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P4" s="32" t="s">
         <v>76</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>4</v>
       </c>
       <c r="B5" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>115</v>
-      </c>
       <c r="D5" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>82</v>
@@ -3415,51 +3415,51 @@
         <v>77</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I5" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="L5" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="N5" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="J5" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>130</v>
-      </c>
       <c r="O5" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P5" s="32" t="s">
         <v>76</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>5</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>82</v>
@@ -3468,51 +3468,51 @@
         <v>77</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J6" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="L6" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="K6" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>162</v>
-      </c>
       <c r="M6" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N6" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P6" s="32" t="s">
         <v>76</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>6</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>82</v>
@@ -3521,51 +3521,51 @@
         <v>77</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J7" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>162</v>
-      </c>
       <c r="M7" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N7" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="O7" s="25" t="s">
         <v>130</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>131</v>
       </c>
       <c r="P7" s="32" t="s">
         <v>76</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>7</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="46" t="s">
         <v>82</v>
@@ -3574,37 +3574,37 @@
         <v>77</v>
       </c>
       <c r="G8" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="M8" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="25" t="s">
         <v>133</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>134</v>
       </c>
       <c r="P8" s="32" t="s">
         <v>76</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/AGIR/Ontologia_AGENTES.xlsx
+++ b/Versão5/AGIR/Ontologia_AGENTES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACBBA2B-D62A-4C0A-906F-20B015D07F1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77522B81-AACC-48EE-B6BD-4C5551964E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="173">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -313,18 +313,6 @@
     <t>Equivalente a</t>
   </si>
   <si>
-    <t>órgão</t>
-  </si>
-  <si>
-    <t>"UFRJ"</t>
-  </si>
-  <si>
-    <t>Projeto.01</t>
-  </si>
-  <si>
-    <t>"UFRJ - Cidade Universitária - RJ"</t>
-  </si>
-  <si>
     <t>CategoriaRvt</t>
   </si>
   <si>
@@ -367,33 +355,6 @@
     <t>Traduções al español e inglês incorporadas. As traduções devem ser constantemente revisadas</t>
   </si>
   <si>
-    <t>Informação</t>
-  </si>
-  <si>
-    <t>Contêiner</t>
-  </si>
-  <si>
-    <t>"Contêiner do Inventário de todas as informações espaciais do Projeto"</t>
-  </si>
-  <si>
-    <t>Requisito.Espacial</t>
-  </si>
-  <si>
-    <t>Requisito.Mobiliário</t>
-  </si>
-  <si>
-    <t>Requisito.Equipamento</t>
-  </si>
-  <si>
-    <t>Requisito.Sistemas</t>
-  </si>
-  <si>
-    <t>Gestão</t>
-  </si>
-  <si>
-    <t>"Instituição de Ensino Superior"</t>
-  </si>
-  <si>
     <t>Agentes</t>
   </si>
   <si>
@@ -562,30 +523,6 @@
     <t>quem.criou</t>
   </si>
   <si>
-    <t>Contêineres</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>[ 5I ]</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>Interdisciplinar</t>
   </si>
   <si>
@@ -593,6 +530,66 @@
   </si>
   <si>
     <t>Agênticos</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>agente.de</t>
+  </si>
+  <si>
+    <t>"Projeto_A"</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Agente</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Inteligência</t>
+  </si>
+  <si>
+    <t>Define um agente utilizado no Projeto.</t>
+  </si>
+  <si>
+    <t>Linguagem</t>
+  </si>
+  <si>
+    <t>Sintaxe</t>
+  </si>
+  <si>
+    <t>Define uma linguagem utilizada para automatizar tarefas do projeto.</t>
+  </si>
+  <si>
+    <t>Define uma sintaxe utilizada para automatizar tarefas do projeto.</t>
+  </si>
+  <si>
+    <t>Projeto_A</t>
+  </si>
+  <si>
+    <t>"Nome do projeto"</t>
+  </si>
+  <si>
+    <t>"Autor do projeto"</t>
+  </si>
+  <si>
+    <t>"Projeto de arquitetura"</t>
+  </si>
+  <si>
+    <t>"Escola"</t>
+  </si>
+  <si>
+    <t>etapa</t>
+  </si>
+  <si>
+    <t>"Estudo preliminar"</t>
+  </si>
+  <si>
+    <t>API.Agentes</t>
   </si>
 </sst>
 </file>
@@ -683,7 +680,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -782,12 +779,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -805,7 +796,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -866,19 +857,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -917,13 +895,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -939,9 +917,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -984,9 +959,6 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1002,16 +974,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1027,9 +996,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1037,24 +1003,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1063,7 +1020,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1072,7 +1029,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1084,10 +1041,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1098,19 +1055,51 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1210,6 +1199,70 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1254,6 +1307,32 @@
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
   </dxfs>
@@ -1659,305 +1738,305 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="61" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="53" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.3046875" style="61"/>
+    <col min="1" max="1" width="9.28515625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.28515625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="18" t="s">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="51" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="19" t="s">
+      <c r="C1" s="44" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
+      <c r="C2" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="20" t="s">
+      <c r="B3" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
+      <c r="C4" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="20" t="str">
+      <c r="B5" s="19" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="20" t="s">
+      <c r="C5" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="20" t="str">
+      <c r="B6" s="19" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C6" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="20">
+        <f ca="1">NOW()</f>
+        <v>46244.519561111112</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="21">
-        <f ca="1">NOW()</f>
-        <v>46243.449320254629</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="21" t="str">
+      <c r="B20" s="20" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="20" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C21" s="52" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="20" t="s">
+      <c r="C21" s="45" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="20" t="s">
+      <c r="C22" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="20" t="s">
+      <c r="C23" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="52" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="20" t="s">
+      <c r="B24" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="22" t="str">
+      <c r="B25" s="21" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formaliza las clases para agentes.</v>
       </c>
-      <c r="C25" s="52" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="22" t="str">
+      <c r="C25" s="45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="21" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize agent classes.</v>
       </c>
-      <c r="C26" s="52" t="s">
-        <v>93</v>
+      <c r="C26" s="45" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1968,885 +2047,709 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AA7"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.3046875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.53515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.53515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="51.53515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="7.7109375" style="13" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="37.5703125" style="13" customWidth="1"/>
+    <col min="17" max="17" width="42.85546875" style="13" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.69140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.07421875" style="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.69140625" style="60" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="6.53515625" style="35" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.3046875" style="34" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="2"/>
+    <col min="20" max="20" width="6.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="6.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="45.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="31" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="26">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="62" t="s">
+      <c r="R1" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="17" t="s">
+      <c r="S1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="17" t="s">
+      <c r="T1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="U1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="V1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="58" t="s">
+      <c r="W1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="X1" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y1" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z1" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA1" s="50" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="36">
+      <c r="X1" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y1" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z1" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA1" s="43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="33">
         <v>2</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="37" t="s">
+      <c r="B2" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="36" t="str">
+        <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
+        <v>Agênticos</v>
+      </c>
+      <c r="M2" s="36" t="str">
+        <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
+        <v>Agentes</v>
+      </c>
+      <c r="N2" s="36" t="str">
+        <f t="shared" ref="N2:O2" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Humanos</v>
+      </c>
+      <c r="O2" s="36" t="str">
+        <f t="shared" si="2"/>
+        <v>Agente Humano</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="R2" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="38" t="str">
+        <f t="shared" ref="S2:U2" si="3">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Agênticos</v>
+      </c>
+      <c r="T2" s="38" t="str">
+        <f t="shared" si="3"/>
+        <v>Agentes</v>
+      </c>
+      <c r="U2" s="38" t="str">
+        <f t="shared" si="3"/>
+        <v>Humanos</v>
+      </c>
+      <c r="V2" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="W2" s="52" t="str">
+        <f t="shared" ref="W2:W5" si="4">CONCATENATE("Key-AGEN-",A2)</f>
+        <v>Key-AGEN-2</v>
+      </c>
+      <c r="X2" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y2" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z2" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA2" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F2" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="40" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Gestão</v>
-      </c>
-      <c r="M2" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N2" s="40" t="str">
-        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Contêineres</v>
-      </c>
-      <c r="O2" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="P2" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q2" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R2" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="43" t="str">
-        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Gestão</v>
-      </c>
-      <c r="T2" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U2" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="V2" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W2" s="59" t="str">
-        <f>CONCATENATE("Key-AGEN-",A2)</f>
-        <v>Key-AGEN-2</v>
-      </c>
-      <c r="X2" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y2" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z2" s="42" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA2" s="41" t="str">
-        <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="36">
+    </row>
+    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33">
         <v>3</v>
       </c>
-      <c r="B3" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F3" s="38" t="s">
+      <c r="B3" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M3" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N3" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O3" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Espacial</v>
-      </c>
-      <c r="P3" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q3" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R3" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S3" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T3" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U3" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="V3" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W3" s="59" t="str">
-        <f t="shared" ref="W3:W9" si="4">CONCATENATE("Key-AGEN-",A3)</f>
+      <c r="G3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="36" t="str">
+        <f t="shared" ref="L3:M3" si="5">CONCATENATE("", C3)</f>
+        <v>Agênticos</v>
+      </c>
+      <c r="M3" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>Agentes</v>
+      </c>
+      <c r="N3" s="36" t="str">
+        <f t="shared" ref="N3:O3" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+        <v>Artificiais</v>
+      </c>
+      <c r="O3" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>Agente Artificial</v>
+      </c>
+      <c r="P3" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q3" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="R3" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="38" t="str">
+        <f t="shared" ref="S3" si="7">SUBSTITUTE(C3, ".", " ")</f>
+        <v>Agênticos</v>
+      </c>
+      <c r="T3" s="38" t="str">
+        <f t="shared" ref="T3" si="8">SUBSTITUTE(D3, ".", " ")</f>
+        <v>Agentes</v>
+      </c>
+      <c r="U3" s="38" t="str">
+        <f t="shared" ref="U3" si="9">SUBSTITUTE(E3, ".", " ")</f>
+        <v>Artificiais</v>
+      </c>
+      <c r="V3" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="W3" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-3</v>
       </c>
-      <c r="X3" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y3" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="41" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="36">
+      <c r="X3" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y3" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z3" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA3" s="37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33">
         <v>4</v>
       </c>
-      <c r="B4" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F4" s="38" t="s">
+      <c r="B4" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="G4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M4" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N4" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O4" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Mobiliário</v>
-      </c>
-      <c r="P4" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q4" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R4" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S4" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T4" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U4" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="V4" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W4" s="59" t="str">
+      <c r="G4" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="36" t="str">
+        <f t="shared" ref="L4:M5" si="10">CONCATENATE("", C4)</f>
+        <v>Agênticos</v>
+      </c>
+      <c r="M4" s="36" t="str">
+        <f t="shared" ref="M4" si="11">CONCATENATE("", D4)</f>
+        <v>Agentes</v>
+      </c>
+      <c r="N4" s="36" t="str">
+        <f t="shared" ref="N4:O5" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
+        <v>Linguagens</v>
+      </c>
+      <c r="O4" s="36" t="str">
+        <f t="shared" ref="O4" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F4),"."," ")," De "," de "))</f>
+        <v>Gherkin</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q4" s="37" t="str">
+        <f>_xlfn.TRANSLATE(P4,"pt","es")</f>
+        <v>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</v>
+      </c>
+      <c r="R4" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S4" s="38" t="str">
+        <f t="shared" ref="S4:U5" si="14">SUBSTITUTE(C4, ".", " ")</f>
+        <v>Agênticos</v>
+      </c>
+      <c r="T4" s="38" t="str">
+        <f t="shared" ref="T4" si="15">SUBSTITUTE(D4, ".", " ")</f>
+        <v>Agentes</v>
+      </c>
+      <c r="U4" s="38" t="str">
+        <f t="shared" ref="U4" si="16">SUBSTITUTE(E4, ".", " ")</f>
+        <v>Linguagens</v>
+      </c>
+      <c r="V4" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="W4" s="52" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-4</v>
       </c>
-      <c r="X4" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y4" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z4" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="41" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="36">
+      <c r="X4" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y4" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z4" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA4" s="37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="33">
         <v>5</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>163</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M5" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N5" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O5" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Equipamento</v>
-      </c>
-      <c r="P5" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q5" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R5" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S5" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T5" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U5" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="V5" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W5" s="59" t="str">
+      <c r="F5" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>Inteligência</v>
+      </c>
+      <c r="M5" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>API</v>
+      </c>
+      <c r="N5" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>API Agentes</v>
+      </c>
+      <c r="O5" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Agente</v>
+      </c>
+      <c r="P5" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q5" s="37" t="str">
+        <f t="shared" ref="Q5" si="17">_xlfn.TRANSLATE(P5,"pt","es")</f>
+        <v>Define un agente utilizado en el Proyecto.</v>
+      </c>
+      <c r="R5" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S5" s="37" t="str">
+        <f t="shared" si="14"/>
+        <v>Inteligência</v>
+      </c>
+      <c r="T5" s="37" t="str">
+        <f t="shared" si="14"/>
+        <v>API</v>
+      </c>
+      <c r="U5" s="37" t="str">
+        <f t="shared" si="14"/>
+        <v>API Agentes</v>
+      </c>
+      <c r="V5" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="W5" s="52" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-5</v>
       </c>
-      <c r="X5" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="41" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="36">
+      <c r="X5" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y5" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z5" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA5" s="37" t="str">
+        <f t="shared" ref="AA5" si="18">_xlfn.TRANSLATE(P5,"pt","en")</f>
+        <v>Defines an agent used in the Project.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="33">
         <v>6</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="C6" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="38" t="s">
+      <c r="F6" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="36" t="str">
+        <f t="shared" ref="L6:L7" si="19">CONCATENATE("", C6)</f>
+        <v>Inteligência</v>
+      </c>
+      <c r="M6" s="36" t="str">
+        <f t="shared" ref="M6:M7" si="20">CONCATENATE("", D6)</f>
+        <v>API</v>
+      </c>
+      <c r="N6" s="36" t="str">
+        <f t="shared" ref="N6:N7" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
+        <v>API Agentes</v>
+      </c>
+      <c r="O6" s="36" t="str">
+        <f t="shared" ref="O6:O7" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F6),"."," ")," De "," de "))</f>
+        <v>Linguagem</v>
+      </c>
+      <c r="P6" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="F6" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Gestão</v>
-      </c>
-      <c r="M6" s="40" t="str">
-        <f t="shared" si="0"/>
-        <v>Informação</v>
-      </c>
-      <c r="N6" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="O6" s="40" t="str">
-        <f t="shared" si="1"/>
-        <v>Requisito Sistemas</v>
-      </c>
-      <c r="P6" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q6" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="R6" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S6" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Gestão</v>
-      </c>
-      <c r="T6" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Informação</v>
-      </c>
-      <c r="U6" s="43" t="str">
-        <f t="shared" si="2"/>
-        <v>Contêineres</v>
-      </c>
-      <c r="V6" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W6" s="59" t="str">
-        <f t="shared" si="4"/>
+      <c r="Q6" s="37" t="str">
+        <f t="shared" ref="Q6:Q7" si="23">_xlfn.TRANSLATE(P6,"pt","es")</f>
+        <v>Define un lenguaje utilizado para automatizar tareas de proyectos.</v>
+      </c>
+      <c r="R6" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S6" s="37" t="str">
+        <f t="shared" ref="S6:S7" si="24">SUBSTITUTE(C6, ".", " ")</f>
+        <v>Inteligência</v>
+      </c>
+      <c r="T6" s="37" t="str">
+        <f t="shared" ref="T6:T7" si="25">SUBSTITUTE(D6, ".", " ")</f>
+        <v>API</v>
+      </c>
+      <c r="U6" s="37" t="str">
+        <f t="shared" ref="U6:U7" si="26">SUBSTITUTE(E6, ".", " ")</f>
+        <v>API Agentes</v>
+      </c>
+      <c r="V6" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="W6" s="52" t="str">
+        <f t="shared" ref="W6:W7" si="27">CONCATENATE("Key-AGEN-",A6)</f>
         <v>Key-AGEN-6</v>
       </c>
-      <c r="X6" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z6" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="41" t="str">
-        <f t="shared" si="3"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="36">
+      <c r="X6" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y6" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z6" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA6" s="37" t="str">
+        <f t="shared" ref="AA6:AA7" si="28">_xlfn.TRANSLATE(P6,"pt","en")</f>
+        <v>Defines a language used to automate project tasks.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="33">
         <v>7</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="C7" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="G7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L7" s="40" t="str">
-        <f t="shared" ref="L7" si="5">CONCATENATE("", C7)</f>
-        <v>Agênticos</v>
-      </c>
-      <c r="M7" s="40" t="str">
-        <f t="shared" ref="M7" si="6">CONCATENATE("", D7)</f>
-        <v>Agentes</v>
-      </c>
-      <c r="N7" s="40" t="str">
-        <f t="shared" ref="N7:O7" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
-        <v>Humanos</v>
-      </c>
-      <c r="O7" s="40" t="str">
-        <f t="shared" si="7"/>
-        <v>Agente Humano</v>
-      </c>
-      <c r="P7" s="41" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q7" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="R7" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S7" s="43" t="str">
-        <f t="shared" ref="S7:U7" si="8">SUBSTITUTE(C7, ".", " ")</f>
-        <v>Agênticos</v>
-      </c>
-      <c r="T7" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Agentes</v>
-      </c>
-      <c r="U7" s="43" t="str">
-        <f t="shared" si="8"/>
-        <v>Humanos</v>
-      </c>
-      <c r="V7" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W7" s="59" t="str">
-        <f t="shared" si="4"/>
+      <c r="F7" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="36" t="str">
+        <f t="shared" si="19"/>
+        <v>Inteligência</v>
+      </c>
+      <c r="M7" s="36" t="str">
+        <f t="shared" si="20"/>
+        <v>API</v>
+      </c>
+      <c r="N7" s="36" t="str">
+        <f t="shared" si="21"/>
+        <v>API Agentes</v>
+      </c>
+      <c r="O7" s="36" t="str">
+        <f t="shared" si="22"/>
+        <v>Sintaxe</v>
+      </c>
+      <c r="P7" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q7" s="37" t="str">
+        <f t="shared" si="23"/>
+        <v>Define una sintaxis utilizada para automatizar tareas del proyecto.</v>
+      </c>
+      <c r="R7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S7" s="37" t="str">
+        <f t="shared" si="24"/>
+        <v>Inteligência</v>
+      </c>
+      <c r="T7" s="37" t="str">
+        <f t="shared" si="25"/>
+        <v>API</v>
+      </c>
+      <c r="U7" s="37" t="str">
+        <f t="shared" si="26"/>
+        <v>API Agentes</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="W7" s="52" t="str">
+        <f t="shared" si="27"/>
         <v>Key-AGEN-7</v>
       </c>
-      <c r="X7" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z7" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="36">
-        <v>8</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="40" t="str">
-        <f t="shared" ref="L8:M8" si="9">CONCATENATE("", C8)</f>
-        <v>Agênticos</v>
-      </c>
-      <c r="M8" s="40" t="str">
-        <f t="shared" si="9"/>
-        <v>Agentes</v>
-      </c>
-      <c r="N8" s="40" t="str">
-        <f t="shared" ref="N8:O8" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
-        <v>Artificiais</v>
-      </c>
-      <c r="O8" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>Agente Artificial</v>
-      </c>
-      <c r="P8" s="41" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q8" s="41" t="s">
-        <v>121</v>
-      </c>
-      <c r="R8" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S8" s="43" t="str">
-        <f t="shared" ref="S8" si="11">SUBSTITUTE(C8, ".", " ")</f>
-        <v>Agênticos</v>
-      </c>
-      <c r="T8" s="43" t="str">
-        <f t="shared" ref="T8" si="12">SUBSTITUTE(D8, ".", " ")</f>
-        <v>Agentes</v>
-      </c>
-      <c r="U8" s="43" t="str">
-        <f t="shared" ref="U8" si="13">SUBSTITUTE(E8, ".", " ")</f>
-        <v>Artificiais</v>
-      </c>
-      <c r="V8" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W8" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-AGEN-8</v>
-      </c>
-      <c r="X8" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y8" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA8" s="41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="36">
-        <v>9</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="G9" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="40" t="str">
-        <f t="shared" ref="L9" si="14">CONCATENATE("", C9)</f>
-        <v>Agênticos</v>
-      </c>
-      <c r="M9" s="40" t="str">
-        <f t="shared" ref="M9" si="15">CONCATENATE("", D9)</f>
-        <v>Agentes</v>
-      </c>
-      <c r="N9" s="40" t="str">
-        <f t="shared" ref="N9" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
-        <v>Linguagens</v>
-      </c>
-      <c r="O9" s="40" t="str">
-        <f t="shared" ref="O9" si="17">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F9),"."," ")," De "," de "))</f>
-        <v>Gherkin</v>
-      </c>
-      <c r="P9" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q9" s="41" t="str">
-        <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
-        <v>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</v>
-      </c>
-      <c r="R9" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" s="43" t="str">
-        <f t="shared" ref="S9" si="18">SUBSTITUTE(C9, ".", " ")</f>
-        <v>Agênticos</v>
-      </c>
-      <c r="T9" s="43" t="str">
-        <f t="shared" ref="T9" si="19">SUBSTITUTE(D9, ".", " ")</f>
-        <v>Agentes</v>
-      </c>
-      <c r="U9" s="43" t="str">
-        <f t="shared" ref="U9" si="20">SUBSTITUTE(E9, ".", " ")</f>
-        <v>Linguagens</v>
-      </c>
-      <c r="V9" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="W9" s="59" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-AGEN-9</v>
-      </c>
-      <c r="X9" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y9" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="41" t="s">
-        <v>155</v>
+      <c r="X7" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y7" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z7" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA7" s="37" t="str">
+        <f t="shared" si="28"/>
+        <v>Defines a syntax used to automate project tasks.</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B9">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA1:AA2 A2:B2 B3:B4 A3:A7">
+    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7:F1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+  <conditionalFormatting sqref="F1:F4 F8:F1048576">
+    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9 AA8:XFD8 L8:O9 AB9:XFD9">
-    <cfRule type="cellIs" dxfId="9" priority="71" operator="equal">
+  <conditionalFormatting sqref="F2:F4 AA3:XFD3 L3:O4 AB4:XFD4">
+    <cfRule type="cellIs" dxfId="24" priority="75" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="8" priority="626"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="658"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="659"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="660"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="661"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="668"/>
+  <conditionalFormatting sqref="F2:F4">
+    <cfRule type="duplicateValues" dxfId="23" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="672"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA7">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="B5:B7">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F7">
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA5:AA7">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2856,16 +2759,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="10"/>
+    <col min="1" max="1" width="2.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="6" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="6" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -2930,7 +2833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -2992,71 +2895,6 @@
         <v>10</v>
       </c>
       <c r="U2" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="R3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="S3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="U3" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3069,35 +2907,35 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="27">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -3110,46 +2948,12 @@
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="27">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="27">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3160,451 +2964,504 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.15234375" style="49" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" style="47" customWidth="1"/>
-    <col min="4" max="4" width="5.84375" style="47" customWidth="1"/>
-    <col min="5" max="5" width="5.3046875" style="47" customWidth="1"/>
-    <col min="6" max="6" width="3.69140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.15234375" style="47" customWidth="1"/>
-    <col min="8" max="8" width="6.53515625" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.69140625" style="47" customWidth="1"/>
-    <col min="10" max="10" width="10.15234375" style="47" customWidth="1"/>
-    <col min="11" max="11" width="9.84375" style="47" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.69140625" style="47" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.3046875" style="47" customWidth="1"/>
-    <col min="14" max="14" width="3.15234375" style="47" customWidth="1"/>
-    <col min="15" max="15" width="14.15234375" style="47" customWidth="1"/>
-    <col min="16" max="16" width="5.15234375" style="47" customWidth="1"/>
-    <col min="17" max="17" width="49.53515625" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="9.3046875" style="47"/>
+    <col min="1" max="1" width="2.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="40" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" style="40" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" style="40" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="40" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="40" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="40" customWidth="1"/>
+    <col min="14" max="14" width="3.140625" style="40" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="40" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" style="40" customWidth="1"/>
+    <col min="17" max="17" width="49.5703125" style="40" customWidth="1"/>
+    <col min="18" max="16384" width="9.28515625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:17" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="56">
-        <v>1</v>
-      </c>
-      <c r="B2" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="44" t="s">
+    <row r="2" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="49">
+        <v>2</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="P2" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q2" s="23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="49">
+        <v>3</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H3" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="K3" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="L3" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M3" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="N3" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O3" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P3" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="49">
+        <v>4</v>
+      </c>
+      <c r="B4" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="32" t="s">
+      <c r="C4" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="I2" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="32" t="s">
+      <c r="G4" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="K4" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M4" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="N4" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O4" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q4" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="49">
+        <v>5</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P5" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="O2" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="P2" s="32" t="s">
+    </row>
+    <row r="6" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="49">
+        <v>6</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="P6" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="56">
-        <v>2</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="C3" s="38" t="s">
+      <c r="Q6" s="23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="49">
+        <v>7</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I7" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="32" t="s">
+      <c r="J7" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="49">
+        <v>8</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="H3" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="J3" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="K3" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="L3" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="M3" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="O3" s="25" t="s">
+      <c r="G8" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M8" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="P3" s="32" t="s">
+      <c r="N8" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O8" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="P8" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="25" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="56">
-        <v>3</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="32" t="s">
+      <c r="Q8" s="23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="49">
+        <v>9</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="J4" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="L4" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="M4" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="O4" s="25" t="s">
+      <c r="G9" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="M9" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="N9" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="56">
-        <v>4</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I5" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="J5" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="L5" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>136</v>
-      </c>
-      <c r="P5" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="56">
-        <v>5</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I6" s="25" t="s">
-        <v>126</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="K6" s="25" t="s">
+      <c r="Q9" s="23" t="s">
         <v>144</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="O6" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="P6" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q6" s="25" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="56">
-        <v>6</v>
-      </c>
-      <c r="B7" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="H7" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I7" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="K7" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="O7" s="25" t="s">
-        <v>130</v>
-      </c>
-      <c r="P7" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q7" s="25" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="56">
-        <v>7</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="H8" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="O8" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="P8" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q8" s="25" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
